--- a/data/temp11.xlsx
+++ b/data/temp11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{890D5EEC-EFD9-4B8C-B843-D6B28C817EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C137FF6-D0AB-42FE-A80F-BBD98D5476A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45" yWindow="60" windowWidth="38355" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="국내생산 계획" sheetId="1" r:id="rId1"/>
@@ -2284,14 +2284,14 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color indexed="64"/>
-      </right>
+      </left>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2303,7 +2303,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2344,6 +2344,15 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2353,23 +2362,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2749,48 +2755,48 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
     </row>
     <row r="3" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
     </row>
     <row r="4" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
@@ -2813,26 +2819,26 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="18"/>
     </row>
     <row r="6" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N6" s="16" t="s">
+      <c r="N6" s="19" t="s">
         <v>284</v>
       </c>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
     </row>
     <row r="7" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3187,7 +3193,7 @@
       <c r="A20" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="2"/>
@@ -3213,7 +3219,7 @@
       <c r="A21" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="2"/>
@@ -3236,25 +3242,25 @@
       <c r="T21" s="3"/>
     </row>
     <row r="22" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
-      <c r="P22" s="18"/>
-      <c r="Q22" s="19"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="3" t="s">
@@ -3265,7 +3271,7 @@
       <c r="A23" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="22" t="s">
         <v>208</v>
       </c>
       <c r="C23" s="2"/>
@@ -3764,7 +3770,7 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
+      <c r="E42" s="22"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -3790,7 +3796,7 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+      <c r="E43" s="22"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -3808,25 +3814,25 @@
       <c r="T43" s="3"/>
     </row>
     <row r="44" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="18"/>
-      <c r="O44" s="18"/>
-      <c r="P44" s="18"/>
-      <c r="Q44" s="19"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="23"/>
+      <c r="K44" s="23"/>
+      <c r="L44" s="23"/>
+      <c r="M44" s="23"/>
+      <c r="N44" s="23"/>
+      <c r="O44" s="23"/>
+      <c r="P44" s="23"/>
+      <c r="Q44" s="23"/>
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
       <c r="T44" s="3" t="s">
@@ -3842,7 +3848,7 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
+      <c r="E45" s="22"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -3868,7 +3874,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
+      <c r="E46" s="22"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -3894,7 +3900,7 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
+      <c r="E47" s="22"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -3920,7 +3926,7 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
+      <c r="E48" s="22"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -3946,7 +3952,7 @@
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
+      <c r="E49" s="22"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -3972,7 +3978,7 @@
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
+      <c r="E50" s="22"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -4388,7 +4394,7 @@
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
+      <c r="E66" s="22"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -4414,7 +4420,7 @@
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
+      <c r="E67" s="22"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -4432,25 +4438,25 @@
       <c r="T67" s="3"/>
     </row>
     <row r="68" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="17" t="s">
+      <c r="A68" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
-      <c r="H68" s="18"/>
-      <c r="I68" s="18"/>
-      <c r="J68" s="18"/>
-      <c r="K68" s="18"/>
-      <c r="L68" s="18"/>
-      <c r="M68" s="18"/>
-      <c r="N68" s="18"/>
-      <c r="O68" s="18"/>
-      <c r="P68" s="18"/>
-      <c r="Q68" s="19"/>
+      <c r="B68" s="15"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="23"/>
+      <c r="G68" s="23"/>
+      <c r="H68" s="23"/>
+      <c r="I68" s="23"/>
+      <c r="J68" s="23"/>
+      <c r="K68" s="23"/>
+      <c r="L68" s="23"/>
+      <c r="M68" s="23"/>
+      <c r="N68" s="23"/>
+      <c r="O68" s="23"/>
+      <c r="P68" s="23"/>
+      <c r="Q68" s="23"/>
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
       <c r="T68" s="3" t="s">
@@ -4466,7 +4472,7 @@
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
+      <c r="E69" s="22"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -4492,7 +4498,7 @@
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
+      <c r="E70" s="22"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -4518,7 +4524,7 @@
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
+      <c r="E71" s="22"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -4544,7 +4550,7 @@
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
+      <c r="E72" s="22"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -5246,7 +5252,7 @@
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
+      <c r="E99" s="22"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -5272,7 +5278,7 @@
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
+      <c r="E100" s="22"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -5298,7 +5304,7 @@
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
+      <c r="E101" s="22"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -5316,25 +5322,25 @@
       <c r="T101" s="3"/>
     </row>
     <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="17" t="s">
+      <c r="A102" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B102" s="18"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="18"/>
-      <c r="E102" s="18"/>
-      <c r="F102" s="18"/>
-      <c r="G102" s="18"/>
-      <c r="H102" s="18"/>
-      <c r="I102" s="18"/>
-      <c r="J102" s="18"/>
-      <c r="K102" s="18"/>
-      <c r="L102" s="18"/>
-      <c r="M102" s="18"/>
-      <c r="N102" s="18"/>
-      <c r="O102" s="18"/>
-      <c r="P102" s="18"/>
-      <c r="Q102" s="19"/>
+      <c r="B102" s="15"/>
+      <c r="C102" s="15"/>
+      <c r="D102" s="15"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="23"/>
+      <c r="H102" s="23"/>
+      <c r="I102" s="23"/>
+      <c r="J102" s="23"/>
+      <c r="K102" s="23"/>
+      <c r="L102" s="23"/>
+      <c r="M102" s="23"/>
+      <c r="N102" s="23"/>
+      <c r="O102" s="23"/>
+      <c r="P102" s="23"/>
+      <c r="Q102" s="23"/>
       <c r="R102" s="2"/>
       <c r="S102" s="2"/>
       <c r="T102" s="3" t="s">
@@ -5350,7 +5356,7 @@
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
+      <c r="E103" s="22"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5376,7 +5382,7 @@
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
+      <c r="E104" s="22"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5402,7 +5408,7 @@
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
+      <c r="E105" s="22"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5428,7 +5434,7 @@
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
+      <c r="E106" s="22"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -5454,7 +5460,7 @@
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
+      <c r="E107" s="22"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -5610,7 +5616,7 @@
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
+      <c r="E113" s="22"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
@@ -5636,7 +5642,7 @@
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
+      <c r="E114" s="22"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
@@ -5654,25 +5660,25 @@
       <c r="T114" s="3"/>
     </row>
     <row r="115" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="17" t="s">
+      <c r="A115" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B115" s="18"/>
-      <c r="C115" s="18"/>
-      <c r="D115" s="18"/>
-      <c r="E115" s="18"/>
-      <c r="F115" s="18"/>
-      <c r="G115" s="18"/>
-      <c r="H115" s="18"/>
-      <c r="I115" s="18"/>
-      <c r="J115" s="18"/>
-      <c r="K115" s="18"/>
-      <c r="L115" s="18"/>
-      <c r="M115" s="18"/>
-      <c r="N115" s="18"/>
-      <c r="O115" s="18"/>
-      <c r="P115" s="18"/>
-      <c r="Q115" s="19"/>
+      <c r="B115" s="15"/>
+      <c r="C115" s="15"/>
+      <c r="D115" s="15"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="23"/>
+      <c r="G115" s="23"/>
+      <c r="H115" s="23"/>
+      <c r="I115" s="23"/>
+      <c r="J115" s="23"/>
+      <c r="K115" s="23"/>
+      <c r="L115" s="23"/>
+      <c r="M115" s="23"/>
+      <c r="N115" s="23"/>
+      <c r="O115" s="23"/>
+      <c r="P115" s="23"/>
+      <c r="Q115" s="23"/>
       <c r="R115" s="2"/>
       <c r="S115" s="2"/>
       <c r="T115" s="3" t="s">
@@ -5688,7 +5694,7 @@
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
+      <c r="E116" s="22"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -5714,7 +5720,7 @@
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
+      <c r="E117" s="22"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -5740,7 +5746,7 @@
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
+      <c r="E118" s="22"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -5766,7 +5772,7 @@
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
+      <c r="E119" s="22"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -5792,7 +5798,7 @@
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
+      <c r="E120" s="22"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -6000,7 +6006,7 @@
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
+      <c r="E128" s="22"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -6026,7 +6032,7 @@
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
+      <c r="E129" s="22"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -6052,7 +6058,7 @@
       </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
+      <c r="E130" s="22"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -6070,25 +6076,25 @@
       <c r="T130" s="3"/>
     </row>
     <row r="131" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="17" t="s">
+      <c r="A131" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B131" s="18"/>
-      <c r="C131" s="18"/>
-      <c r="D131" s="18"/>
-      <c r="E131" s="18"/>
-      <c r="F131" s="18"/>
-      <c r="G131" s="18"/>
-      <c r="H131" s="18"/>
-      <c r="I131" s="18"/>
-      <c r="J131" s="18"/>
-      <c r="K131" s="18"/>
-      <c r="L131" s="18"/>
-      <c r="M131" s="18"/>
-      <c r="N131" s="18"/>
-      <c r="O131" s="18"/>
-      <c r="P131" s="18"/>
-      <c r="Q131" s="19"/>
+      <c r="B131" s="15"/>
+      <c r="C131" s="15"/>
+      <c r="D131" s="15"/>
+      <c r="E131" s="15"/>
+      <c r="F131" s="23"/>
+      <c r="G131" s="23"/>
+      <c r="H131" s="23"/>
+      <c r="I131" s="23"/>
+      <c r="J131" s="23"/>
+      <c r="K131" s="23"/>
+      <c r="L131" s="23"/>
+      <c r="M131" s="23"/>
+      <c r="N131" s="23"/>
+      <c r="O131" s="23"/>
+      <c r="P131" s="23"/>
+      <c r="Q131" s="23"/>
       <c r="R131" s="2"/>
       <c r="S131" s="2"/>
       <c r="T131" s="3" t="s">
@@ -6104,7 +6110,7 @@
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
+      <c r="E132" s="22"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -6130,7 +6136,7 @@
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
+      <c r="E133" s="22"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -6156,7 +6162,7 @@
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
+      <c r="E134" s="22"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -6182,7 +6188,7 @@
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
+      <c r="E135" s="22"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -6208,7 +6214,7 @@
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
-      <c r="E136" s="2"/>
+      <c r="E136" s="22"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -6226,25 +6232,25 @@
       <c r="T136" s="3"/>
     </row>
     <row r="137" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="17" t="s">
+      <c r="A137" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B137" s="18"/>
-      <c r="C137" s="18"/>
-      <c r="D137" s="18"/>
-      <c r="E137" s="18"/>
-      <c r="F137" s="18"/>
-      <c r="G137" s="18"/>
-      <c r="H137" s="18"/>
-      <c r="I137" s="18"/>
-      <c r="J137" s="18"/>
-      <c r="K137" s="18"/>
-      <c r="L137" s="18"/>
-      <c r="M137" s="18"/>
-      <c r="N137" s="18"/>
-      <c r="O137" s="18"/>
-      <c r="P137" s="18"/>
-      <c r="Q137" s="19"/>
+      <c r="B137" s="15"/>
+      <c r="C137" s="15"/>
+      <c r="D137" s="15"/>
+      <c r="E137" s="15"/>
+      <c r="F137" s="23"/>
+      <c r="G137" s="23"/>
+      <c r="H137" s="23"/>
+      <c r="I137" s="23"/>
+      <c r="J137" s="23"/>
+      <c r="K137" s="23"/>
+      <c r="L137" s="23"/>
+      <c r="M137" s="23"/>
+      <c r="N137" s="23"/>
+      <c r="O137" s="23"/>
+      <c r="P137" s="23"/>
+      <c r="Q137" s="23"/>
       <c r="R137" s="2"/>
       <c r="S137" s="2"/>
       <c r="T137" s="3" t="s">
@@ -6260,7 +6266,7 @@
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
+      <c r="E138" s="22"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -6286,7 +6292,7 @@
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
-      <c r="E139" s="2"/>
+      <c r="E139" s="22"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6304,25 +6310,25 @@
       <c r="T139" s="3"/>
     </row>
     <row r="140" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="17" t="s">
+      <c r="A140" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B140" s="18"/>
-      <c r="C140" s="18"/>
-      <c r="D140" s="18"/>
-      <c r="E140" s="18"/>
-      <c r="F140" s="18"/>
-      <c r="G140" s="18"/>
-      <c r="H140" s="18"/>
-      <c r="I140" s="18"/>
-      <c r="J140" s="18"/>
-      <c r="K140" s="18"/>
-      <c r="L140" s="18"/>
-      <c r="M140" s="18"/>
-      <c r="N140" s="18"/>
-      <c r="O140" s="18"/>
-      <c r="P140" s="18"/>
-      <c r="Q140" s="19"/>
+      <c r="B140" s="15"/>
+      <c r="C140" s="15"/>
+      <c r="D140" s="15"/>
+      <c r="E140" s="15"/>
+      <c r="F140" s="23"/>
+      <c r="G140" s="23"/>
+      <c r="H140" s="23"/>
+      <c r="I140" s="23"/>
+      <c r="J140" s="23"/>
+      <c r="K140" s="23"/>
+      <c r="L140" s="23"/>
+      <c r="M140" s="23"/>
+      <c r="N140" s="23"/>
+      <c r="O140" s="23"/>
+      <c r="P140" s="23"/>
+      <c r="Q140" s="23"/>
       <c r="R140" s="2"/>
       <c r="S140" s="2"/>
       <c r="T140" s="3" t="s">
@@ -6338,7 +6344,7 @@
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
+      <c r="E141" s="22"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -6364,7 +6370,7 @@
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
+      <c r="E142" s="22"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -6390,7 +6396,7 @@
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
+      <c r="E143" s="22"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -6416,7 +6422,7 @@
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
+      <c r="E144" s="22"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -6442,7 +6448,7 @@
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
+      <c r="E145" s="22"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -6468,7 +6474,7 @@
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
+      <c r="E146" s="22"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -7118,7 +7124,7 @@
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
-      <c r="E171" s="2"/>
+      <c r="E171" s="22"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
@@ -7144,7 +7150,7 @@
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
+      <c r="E172" s="22"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
@@ -7162,25 +7168,25 @@
       <c r="T172" s="3"/>
     </row>
     <row r="173" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="17" t="s">
+      <c r="A173" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B173" s="18"/>
-      <c r="C173" s="18"/>
-      <c r="D173" s="18"/>
-      <c r="E173" s="18"/>
-      <c r="F173" s="18"/>
-      <c r="G173" s="18"/>
-      <c r="H173" s="18"/>
-      <c r="I173" s="18"/>
-      <c r="J173" s="18"/>
-      <c r="K173" s="18"/>
-      <c r="L173" s="18"/>
-      <c r="M173" s="18"/>
-      <c r="N173" s="18"/>
-      <c r="O173" s="18"/>
-      <c r="P173" s="18"/>
-      <c r="Q173" s="19"/>
+      <c r="B173" s="15"/>
+      <c r="C173" s="15"/>
+      <c r="D173" s="15"/>
+      <c r="E173" s="15"/>
+      <c r="F173" s="23"/>
+      <c r="G173" s="23"/>
+      <c r="H173" s="23"/>
+      <c r="I173" s="23"/>
+      <c r="J173" s="23"/>
+      <c r="K173" s="23"/>
+      <c r="L173" s="23"/>
+      <c r="M173" s="23"/>
+      <c r="N173" s="23"/>
+      <c r="O173" s="23"/>
+      <c r="P173" s="23"/>
+      <c r="Q173" s="23"/>
       <c r="R173" s="2"/>
       <c r="S173" s="2"/>
       <c r="T173" s="3" t="s">
@@ -7196,7 +7202,7 @@
       </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
-      <c r="E174" s="2"/>
+      <c r="E174" s="22"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
@@ -7222,7 +7228,7 @@
       </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
-      <c r="E175" s="2"/>
+      <c r="E175" s="22"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
@@ -7248,7 +7254,7 @@
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
-      <c r="E176" s="2"/>
+      <c r="E176" s="22"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
@@ -7274,7 +7280,7 @@
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
-      <c r="E177" s="2"/>
+      <c r="E177" s="22"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
@@ -7300,7 +7306,7 @@
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
-      <c r="E178" s="2"/>
+      <c r="E178" s="22"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
@@ -7326,7 +7332,7 @@
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
-      <c r="E179" s="2"/>
+      <c r="E179" s="22"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
@@ -7352,7 +7358,7 @@
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
-      <c r="E180" s="2"/>
+      <c r="E180" s="22"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
@@ -7872,7 +7878,7 @@
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
+      <c r="E200" s="22"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
@@ -7898,7 +7904,7 @@
       </c>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
-      <c r="E201" s="2"/>
+      <c r="E201" s="22"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
@@ -7916,25 +7922,25 @@
       <c r="T201" s="3"/>
     </row>
     <row r="202" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="17" t="s">
+      <c r="A202" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B202" s="18"/>
-      <c r="C202" s="18"/>
-      <c r="D202" s="18"/>
-      <c r="E202" s="18"/>
-      <c r="F202" s="18"/>
-      <c r="G202" s="18"/>
-      <c r="H202" s="18"/>
-      <c r="I202" s="18"/>
-      <c r="J202" s="18"/>
-      <c r="K202" s="18"/>
-      <c r="L202" s="18"/>
-      <c r="M202" s="18"/>
-      <c r="N202" s="18"/>
-      <c r="O202" s="18"/>
-      <c r="P202" s="18"/>
-      <c r="Q202" s="19"/>
+      <c r="B202" s="15"/>
+      <c r="C202" s="15"/>
+      <c r="D202" s="15"/>
+      <c r="E202" s="15"/>
+      <c r="F202" s="23"/>
+      <c r="G202" s="23"/>
+      <c r="H202" s="23"/>
+      <c r="I202" s="23"/>
+      <c r="J202" s="23"/>
+      <c r="K202" s="23"/>
+      <c r="L202" s="23"/>
+      <c r="M202" s="23"/>
+      <c r="N202" s="23"/>
+      <c r="O202" s="23"/>
+      <c r="P202" s="23"/>
+      <c r="Q202" s="23"/>
       <c r="R202" s="2"/>
       <c r="S202" s="2"/>
       <c r="T202" s="3" t="s">
@@ -7950,7 +7956,7 @@
       </c>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
-      <c r="E203" s="2"/>
+      <c r="E203" s="22"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
@@ -7976,7 +7982,7 @@
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
+      <c r="E204" s="22"/>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
@@ -8002,7 +8008,7 @@
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
+      <c r="E205" s="22"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
@@ -8028,7 +8034,7 @@
       </c>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
-      <c r="E206" s="2"/>
+      <c r="E206" s="22"/>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
@@ -8054,7 +8060,7 @@
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
-      <c r="E207" s="2"/>
+      <c r="E207" s="22"/>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
@@ -8080,7 +8086,7 @@
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
-      <c r="E208" s="2"/>
+      <c r="E208" s="22"/>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
@@ -8392,7 +8398,7 @@
       </c>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
+      <c r="E220" s="22"/>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
@@ -8418,7 +8424,7 @@
       </c>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
+      <c r="E221" s="22"/>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
@@ -8444,7 +8450,7 @@
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
+      <c r="E222" s="22"/>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
@@ -8462,25 +8468,25 @@
       <c r="T222" s="3"/>
     </row>
     <row r="223" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="17" t="s">
+      <c r="A223" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="B223" s="18"/>
-      <c r="C223" s="18"/>
-      <c r="D223" s="18"/>
-      <c r="E223" s="18"/>
-      <c r="F223" s="18"/>
-      <c r="G223" s="18"/>
-      <c r="H223" s="18"/>
-      <c r="I223" s="18"/>
-      <c r="J223" s="18"/>
-      <c r="K223" s="18"/>
-      <c r="L223" s="18"/>
-      <c r="M223" s="18"/>
-      <c r="N223" s="18"/>
-      <c r="O223" s="18"/>
-      <c r="P223" s="18"/>
-      <c r="Q223" s="19"/>
+      <c r="B223" s="15"/>
+      <c r="C223" s="15"/>
+      <c r="D223" s="15"/>
+      <c r="E223" s="15"/>
+      <c r="F223" s="23"/>
+      <c r="G223" s="23"/>
+      <c r="H223" s="23"/>
+      <c r="I223" s="23"/>
+      <c r="J223" s="23"/>
+      <c r="K223" s="23"/>
+      <c r="L223" s="23"/>
+      <c r="M223" s="23"/>
+      <c r="N223" s="23"/>
+      <c r="O223" s="23"/>
+      <c r="P223" s="23"/>
+      <c r="Q223" s="23"/>
       <c r="R223" s="2"/>
       <c r="S223" s="2"/>
       <c r="T223" s="3" t="s">
@@ -8496,7 +8502,7 @@
       </c>
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
-      <c r="E224" s="2"/>
+      <c r="E224" s="22"/>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
@@ -8522,7 +8528,7 @@
       </c>
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
-      <c r="E225" s="2"/>
+      <c r="E225" s="22"/>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
@@ -8548,7 +8554,7 @@
       </c>
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
-      <c r="E226" s="2"/>
+      <c r="E226" s="22"/>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
@@ -8574,7 +8580,7 @@
       </c>
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
-      <c r="E227" s="2"/>
+      <c r="E227" s="22"/>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
@@ -8600,7 +8606,7 @@
       </c>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
-      <c r="E228" s="2"/>
+      <c r="E228" s="22"/>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
@@ -8626,7 +8632,7 @@
       </c>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
-      <c r="E229" s="2"/>
+      <c r="E229" s="22"/>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
@@ -8652,7 +8658,7 @@
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
-      <c r="E230" s="2"/>
+      <c r="E230" s="22"/>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
@@ -8938,7 +8944,7 @@
       </c>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
-      <c r="E241" s="2"/>
+      <c r="E241" s="22"/>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
@@ -8964,7 +8970,7 @@
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
-      <c r="E242" s="2"/>
+      <c r="E242" s="22"/>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
@@ -8990,7 +8996,7 @@
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
-      <c r="E243" s="2"/>
+      <c r="E243" s="22"/>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
@@ -9008,25 +9014,25 @@
       <c r="T243" s="3"/>
     </row>
     <row r="244" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="17" t="s">
+      <c r="A244" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="B244" s="18"/>
-      <c r="C244" s="18"/>
-      <c r="D244" s="18"/>
-      <c r="E244" s="18"/>
-      <c r="F244" s="18"/>
-      <c r="G244" s="18"/>
-      <c r="H244" s="18"/>
-      <c r="I244" s="18"/>
-      <c r="J244" s="18"/>
-      <c r="K244" s="18"/>
-      <c r="L244" s="18"/>
-      <c r="M244" s="18"/>
-      <c r="N244" s="18"/>
-      <c r="O244" s="18"/>
-      <c r="P244" s="18"/>
-      <c r="Q244" s="19"/>
+      <c r="B244" s="15"/>
+      <c r="C244" s="15"/>
+      <c r="D244" s="15"/>
+      <c r="E244" s="15"/>
+      <c r="F244" s="23"/>
+      <c r="G244" s="23"/>
+      <c r="H244" s="23"/>
+      <c r="I244" s="23"/>
+      <c r="J244" s="23"/>
+      <c r="K244" s="23"/>
+      <c r="L244" s="23"/>
+      <c r="M244" s="23"/>
+      <c r="N244" s="23"/>
+      <c r="O244" s="23"/>
+      <c r="P244" s="23"/>
+      <c r="Q244" s="23"/>
       <c r="R244" s="2"/>
       <c r="S244" s="2"/>
       <c r="T244" s="3" t="s">
@@ -9042,7 +9048,7 @@
       </c>
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
+      <c r="E245" s="22"/>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
@@ -9068,7 +9074,7 @@
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
-      <c r="E246" s="2"/>
+      <c r="E246" s="22"/>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
@@ -9094,7 +9100,7 @@
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
-      <c r="E247" s="2"/>
+      <c r="E247" s="22"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
@@ -9120,7 +9126,7 @@
       </c>
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
-      <c r="E248" s="2"/>
+      <c r="E248" s="22"/>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
@@ -9146,7 +9152,7 @@
       </c>
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
+      <c r="E249" s="22"/>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
@@ -9172,7 +9178,7 @@
       </c>
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
-      <c r="E250" s="2"/>
+      <c r="E250" s="22"/>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
@@ -9354,7 +9360,7 @@
       </c>
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
-      <c r="E257" s="2"/>
+      <c r="E257" s="22"/>
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
@@ -9380,7 +9386,7 @@
       </c>
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
-      <c r="E258" s="2"/>
+      <c r="E258" s="22"/>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
@@ -9398,25 +9404,25 @@
       <c r="T258" s="3"/>
     </row>
     <row r="259" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="17" t="s">
+      <c r="A259" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B259" s="18"/>
-      <c r="C259" s="18"/>
-      <c r="D259" s="18"/>
-      <c r="E259" s="18"/>
-      <c r="F259" s="18"/>
-      <c r="G259" s="18"/>
-      <c r="H259" s="18"/>
-      <c r="I259" s="18"/>
-      <c r="J259" s="18"/>
-      <c r="K259" s="18"/>
-      <c r="L259" s="18"/>
-      <c r="M259" s="18"/>
-      <c r="N259" s="18"/>
-      <c r="O259" s="18"/>
-      <c r="P259" s="18"/>
-      <c r="Q259" s="19"/>
+      <c r="B259" s="15"/>
+      <c r="C259" s="15"/>
+      <c r="D259" s="15"/>
+      <c r="E259" s="15"/>
+      <c r="F259" s="23"/>
+      <c r="G259" s="23"/>
+      <c r="H259" s="23"/>
+      <c r="I259" s="23"/>
+      <c r="J259" s="23"/>
+      <c r="K259" s="23"/>
+      <c r="L259" s="23"/>
+      <c r="M259" s="23"/>
+      <c r="N259" s="23"/>
+      <c r="O259" s="23"/>
+      <c r="P259" s="23"/>
+      <c r="Q259" s="23"/>
       <c r="R259" s="2"/>
       <c r="S259" s="2"/>
       <c r="T259" s="3" t="s">
@@ -9432,7 +9438,7 @@
       </c>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
-      <c r="E260" s="2"/>
+      <c r="E260" s="22"/>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
@@ -9458,7 +9464,7 @@
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
-      <c r="E261" s="2"/>
+      <c r="E261" s="22"/>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
@@ -9484,7 +9490,7 @@
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
-      <c r="E262" s="2"/>
+      <c r="E262" s="22"/>
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
@@ -9510,7 +9516,7 @@
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
-      <c r="E263" s="2"/>
+      <c r="E263" s="22"/>
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
@@ -9536,7 +9542,7 @@
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
-      <c r="E264" s="2"/>
+      <c r="E264" s="22"/>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
@@ -9822,7 +9828,7 @@
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
-      <c r="E275" s="2"/>
+      <c r="E275" s="22"/>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
@@ -9848,7 +9854,7 @@
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
-      <c r="E276" s="2"/>
+      <c r="E276" s="22"/>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
@@ -9866,25 +9872,25 @@
       <c r="T276" s="3"/>
     </row>
     <row r="277" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="17" t="s">
+      <c r="A277" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="B277" s="18"/>
-      <c r="C277" s="18"/>
-      <c r="D277" s="18"/>
-      <c r="E277" s="18"/>
-      <c r="F277" s="18"/>
-      <c r="G277" s="18"/>
-      <c r="H277" s="18"/>
-      <c r="I277" s="18"/>
-      <c r="J277" s="18"/>
-      <c r="K277" s="18"/>
-      <c r="L277" s="18"/>
-      <c r="M277" s="18"/>
-      <c r="N277" s="18"/>
-      <c r="O277" s="18"/>
-      <c r="P277" s="18"/>
-      <c r="Q277" s="19"/>
+      <c r="B277" s="15"/>
+      <c r="C277" s="15"/>
+      <c r="D277" s="15"/>
+      <c r="E277" s="15"/>
+      <c r="F277" s="23"/>
+      <c r="G277" s="23"/>
+      <c r="H277" s="23"/>
+      <c r="I277" s="23"/>
+      <c r="J277" s="23"/>
+      <c r="K277" s="23"/>
+      <c r="L277" s="23"/>
+      <c r="M277" s="23"/>
+      <c r="N277" s="23"/>
+      <c r="O277" s="23"/>
+      <c r="P277" s="23"/>
+      <c r="Q277" s="23"/>
       <c r="R277" s="2"/>
       <c r="S277" s="2"/>
       <c r="T277" s="3" t="s">
@@ -9900,7 +9906,7 @@
       </c>
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
-      <c r="E278" s="2"/>
+      <c r="E278" s="22"/>
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
@@ -9926,7 +9932,7 @@
       </c>
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
-      <c r="E279" s="2"/>
+      <c r="E279" s="22"/>
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
@@ -9978,7 +9984,7 @@
       </c>
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
-      <c r="E281" s="2"/>
+      <c r="E281" s="22"/>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
@@ -10004,7 +10010,7 @@
       </c>
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
-      <c r="E282" s="2"/>
+      <c r="E282" s="22"/>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
@@ -10030,7 +10036,7 @@
       </c>
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
-      <c r="E283" s="2"/>
+      <c r="E283" s="22"/>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
@@ -10048,25 +10054,25 @@
       <c r="T283" s="3"/>
     </row>
     <row r="284" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="17" t="s">
+      <c r="A284" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="B284" s="18"/>
-      <c r="C284" s="18"/>
-      <c r="D284" s="18"/>
-      <c r="E284" s="18"/>
-      <c r="F284" s="18"/>
-      <c r="G284" s="18"/>
-      <c r="H284" s="18"/>
-      <c r="I284" s="18"/>
-      <c r="J284" s="18"/>
-      <c r="K284" s="18"/>
-      <c r="L284" s="18"/>
-      <c r="M284" s="18"/>
-      <c r="N284" s="18"/>
-      <c r="O284" s="18"/>
-      <c r="P284" s="18"/>
-      <c r="Q284" s="19"/>
+      <c r="B284" s="15"/>
+      <c r="C284" s="15"/>
+      <c r="D284" s="15"/>
+      <c r="E284" s="15"/>
+      <c r="F284" s="23"/>
+      <c r="G284" s="23"/>
+      <c r="H284" s="23"/>
+      <c r="I284" s="23"/>
+      <c r="J284" s="23"/>
+      <c r="K284" s="23"/>
+      <c r="L284" s="23"/>
+      <c r="M284" s="23"/>
+      <c r="N284" s="23"/>
+      <c r="O284" s="23"/>
+      <c r="P284" s="23"/>
+      <c r="Q284" s="23"/>
       <c r="R284" s="2"/>
       <c r="S284" s="2"/>
       <c r="T284" s="3" t="s">
@@ -10081,45 +10087,45 @@
       <c r="C285" s="21"/>
       <c r="D285" s="21"/>
       <c r="E285" s="21"/>
-      <c r="F285" s="21"/>
-      <c r="G285" s="21"/>
-      <c r="H285" s="21"/>
-      <c r="I285" s="21"/>
-      <c r="J285" s="21"/>
-      <c r="K285" s="21"/>
-      <c r="L285" s="21"/>
-      <c r="M285" s="21"/>
-      <c r="N285" s="21"/>
-      <c r="O285" s="21"/>
-      <c r="P285" s="21"/>
-      <c r="Q285" s="22"/>
+      <c r="F285" s="24"/>
+      <c r="G285" s="24"/>
+      <c r="H285" s="24"/>
+      <c r="I285" s="24"/>
+      <c r="J285" s="24"/>
+      <c r="K285" s="24"/>
+      <c r="L285" s="24"/>
+      <c r="M285" s="24"/>
+      <c r="N285" s="24"/>
+      <c r="O285" s="24"/>
+      <c r="P285" s="24"/>
+      <c r="Q285" s="24"/>
       <c r="R285" s="4"/>
       <c r="S285" s="4"/>
       <c r="T285" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A140:Q140"/>
-    <mergeCell ref="A173:Q173"/>
-    <mergeCell ref="A202:Q202"/>
-    <mergeCell ref="A223:Q223"/>
-    <mergeCell ref="A244:Q244"/>
-    <mergeCell ref="A68:Q68"/>
-    <mergeCell ref="A102:Q102"/>
-    <mergeCell ref="A115:Q115"/>
-    <mergeCell ref="A131:Q131"/>
-    <mergeCell ref="A137:Q137"/>
+    <mergeCell ref="A285:E285"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A102:E102"/>
+    <mergeCell ref="A115:E115"/>
+    <mergeCell ref="A131:E131"/>
+    <mergeCell ref="A137:E137"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A173:E173"/>
+    <mergeCell ref="A202:E202"/>
+    <mergeCell ref="A223:E223"/>
+    <mergeCell ref="A244:E244"/>
+    <mergeCell ref="A259:E259"/>
+    <mergeCell ref="A277:E277"/>
+    <mergeCell ref="A284:E284"/>
     <mergeCell ref="A2:T3"/>
     <mergeCell ref="S5:T5"/>
     <mergeCell ref="S6:T6"/>
     <mergeCell ref="N5:R5"/>
     <mergeCell ref="N6:R6"/>
-    <mergeCell ref="A22:Q22"/>
-    <mergeCell ref="A44:Q44"/>
-    <mergeCell ref="A259:Q259"/>
-    <mergeCell ref="A277:Q277"/>
-    <mergeCell ref="A284:Q284"/>
-    <mergeCell ref="A285:Q285"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data/temp11.xlsx
+++ b/data/temp11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C137FF6-D0AB-42FE-A80F-BBD98D5476A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368E3411-E826-4E58-AC93-64E995643D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="60" windowWidth="38355" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="국내생산 계획" sheetId="1" r:id="rId1"/>
@@ -861,10 +861,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>평균 계획량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>계획 수량</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1988,6 +1984,10 @@
   </si>
   <si>
     <t>12월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적정 재고</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2344,6 +2344,21 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2361,21 +2376,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2755,48 +2755,48 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
     </row>
     <row r="3" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
     </row>
     <row r="4" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
@@ -2819,26 +2819,26 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N5" s="19" t="s">
+      <c r="N5" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
+    </row>
+    <row r="6" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="24" t="s">
         <v>283</v>
       </c>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="18"/>
-      <c r="T5" s="18"/>
-    </row>
-    <row r="6" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N6" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="23"/>
     </row>
     <row r="7" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2852,60 +2852,60 @@
         <v>276</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="R8" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>555</v>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="R8" s="9" t="s">
+      <c r="S8" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="T8" s="10" t="s">
         <v>280</v>
-      </c>
-      <c r="T8" s="10" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>3</v>
@@ -2931,7 +2931,7 @@
     </row>
     <row r="10" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>4</v>
@@ -2957,7 +2957,7 @@
     </row>
     <row r="11" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -2983,7 +2983,7 @@
     </row>
     <row r="12" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>6</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="13" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
@@ -3035,7 +3035,7 @@
     </row>
     <row r="14" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
@@ -3061,7 +3061,7 @@
     </row>
     <row r="15" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>9</v>
@@ -3087,7 +3087,7 @@
     </row>
     <row r="16" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>10</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="17" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>11</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="18" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="19" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>13</v>
@@ -3191,9 +3191,9 @@
     </row>
     <row r="20" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B20" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="2"/>
@@ -3217,9 +3217,9 @@
     </row>
     <row r="21" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="B21" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="B21" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="2"/>
@@ -3242,25 +3242,25 @@
       <c r="T21" s="3"/>
     </row>
     <row r="22" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="3" t="s">
@@ -3269,9 +3269,9 @@
     </row>
     <row r="23" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="B23" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="B23" s="14" t="s">
         <v>208</v>
       </c>
       <c r="C23" s="2"/>
@@ -3295,7 +3295,7 @@
     </row>
     <row r="24" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>209</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="25" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>210</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="26" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>211</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="27" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>212</v>
@@ -3399,7 +3399,7 @@
     </row>
     <row r="28" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>213</v>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="29" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>214</v>
@@ -3451,7 +3451,7 @@
     </row>
     <row r="30" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>215</v>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="31" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>216</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="32" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>217</v>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="33" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>218</v>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="34" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>219</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="35" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>220</v>
@@ -3607,7 +3607,7 @@
     </row>
     <row r="36" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>221</v>
@@ -3633,7 +3633,7 @@
     </row>
     <row r="37" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>222</v>
@@ -3659,7 +3659,7 @@
     </row>
     <row r="38" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>223</v>
@@ -3685,7 +3685,7 @@
     </row>
     <row r="39" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>224</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="40" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>225</v>
@@ -3737,7 +3737,7 @@
     </row>
     <row r="41" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>226</v>
@@ -3763,14 +3763,14 @@
     </row>
     <row r="42" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>227</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="22"/>
+      <c r="E42" s="14"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -3789,14 +3789,14 @@
     </row>
     <row r="43" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>228</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="22"/>
+      <c r="E43" s="14"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -3814,25 +3814,25 @@
       <c r="T43" s="3"/>
     </row>
     <row r="44" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="23"/>
-      <c r="J44" s="23"/>
-      <c r="K44" s="23"/>
-      <c r="L44" s="23"/>
-      <c r="M44" s="23"/>
-      <c r="N44" s="23"/>
-      <c r="O44" s="23"/>
-      <c r="P44" s="23"/>
-      <c r="Q44" s="23"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="15"/>
+      <c r="O44" s="15"/>
+      <c r="P44" s="15"/>
+      <c r="Q44" s="15"/>
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
       <c r="T44" s="3" t="s">
@@ -3841,14 +3841,14 @@
     </row>
     <row r="45" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="22"/>
+      <c r="E45" s="14"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -3867,14 +3867,14 @@
     </row>
     <row r="46" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="22"/>
+      <c r="E46" s="14"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -3893,14 +3893,14 @@
     </row>
     <row r="47" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="22"/>
+      <c r="E47" s="14"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -3919,14 +3919,14 @@
     </row>
     <row r="48" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>188</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="22"/>
+      <c r="E48" s="14"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -3945,14 +3945,14 @@
     </row>
     <row r="49" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="22"/>
+      <c r="E49" s="14"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -3971,14 +3971,14 @@
     </row>
     <row r="50" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="22"/>
+      <c r="E50" s="14"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="51" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>191</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="52" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>192</v>
@@ -4049,7 +4049,7 @@
     </row>
     <row r="53" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>193</v>
@@ -4075,7 +4075,7 @@
     </row>
     <row r="54" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>194</v>
@@ -4101,7 +4101,7 @@
     </row>
     <row r="55" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>195</v>
@@ -4127,7 +4127,7 @@
     </row>
     <row r="56" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>196</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="57" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>197</v>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="58" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>198</v>
@@ -4205,7 +4205,7 @@
     </row>
     <row r="59" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>199</v>
@@ -4231,7 +4231,7 @@
     </row>
     <row r="60" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>200</v>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="61" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>201</v>
@@ -4283,7 +4283,7 @@
     </row>
     <row r="62" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>202</v>
@@ -4309,7 +4309,7 @@
     </row>
     <row r="63" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>203</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="64" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>204</v>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="65" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>205</v>
@@ -4387,14 +4387,14 @@
     </row>
     <row r="66" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>206</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
-      <c r="E66" s="22"/>
+      <c r="E66" s="14"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -4413,14 +4413,14 @@
     </row>
     <row r="67" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
-      <c r="E67" s="22"/>
+      <c r="E67" s="14"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -4438,25 +4438,25 @@
       <c r="T67" s="3"/>
     </row>
     <row r="68" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="23"/>
-      <c r="G68" s="23"/>
-      <c r="H68" s="23"/>
-      <c r="I68" s="23"/>
-      <c r="J68" s="23"/>
-      <c r="K68" s="23"/>
-      <c r="L68" s="23"/>
-      <c r="M68" s="23"/>
-      <c r="N68" s="23"/>
-      <c r="O68" s="23"/>
-      <c r="P68" s="23"/>
-      <c r="Q68" s="23"/>
+      <c r="A68" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="15"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+      <c r="L68" s="15"/>
+      <c r="M68" s="15"/>
+      <c r="N68" s="15"/>
+      <c r="O68" s="15"/>
+      <c r="P68" s="15"/>
+      <c r="Q68" s="15"/>
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
       <c r="T68" s="3" t="s">
@@ -4465,14 +4465,14 @@
     </row>
     <row r="69" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="22"/>
+      <c r="E69" s="14"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -4491,14 +4491,14 @@
     </row>
     <row r="70" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="22"/>
+      <c r="E70" s="14"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -4517,14 +4517,14 @@
     </row>
     <row r="71" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="22"/>
+      <c r="E71" s="14"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -4543,14 +4543,14 @@
     </row>
     <row r="72" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="22"/>
+      <c r="E72" s="14"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -4569,7 +4569,7 @@
     </row>
     <row r="73" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>155</v>
@@ -4595,7 +4595,7 @@
     </row>
     <row r="74" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>156</v>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="75" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>157</v>
@@ -4647,7 +4647,7 @@
     </row>
     <row r="76" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>158</v>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="77" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>159</v>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="78" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>160</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="79" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>161</v>
@@ -4751,7 +4751,7 @@
     </row>
     <row r="80" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>162</v>
@@ -4777,7 +4777,7 @@
     </row>
     <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>163</v>
@@ -4803,7 +4803,7 @@
     </row>
     <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>164</v>
@@ -4829,7 +4829,7 @@
     </row>
     <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>165</v>
@@ -4855,7 +4855,7 @@
     </row>
     <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>166</v>
@@ -4881,7 +4881,7 @@
     </row>
     <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>167</v>
@@ -4907,7 +4907,7 @@
     </row>
     <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>168</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>169</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>170</v>
@@ -4985,7 +4985,7 @@
     </row>
     <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>171</v>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>172</v>
@@ -5037,7 +5037,7 @@
     </row>
     <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>173</v>
@@ -5063,7 +5063,7 @@
     </row>
     <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>174</v>
@@ -5089,7 +5089,7 @@
     </row>
     <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>175</v>
@@ -5115,7 +5115,7 @@
     </row>
     <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>176</v>
@@ -5141,7 +5141,7 @@
     </row>
     <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>177</v>
@@ -5167,7 +5167,7 @@
     </row>
     <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>178</v>
@@ -5193,7 +5193,7 @@
     </row>
     <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>179</v>
@@ -5219,7 +5219,7 @@
     </row>
     <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>180</v>
@@ -5245,14 +5245,14 @@
     </row>
     <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="22"/>
+      <c r="E99" s="14"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -5271,14 +5271,14 @@
     </row>
     <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="22"/>
+      <c r="E100" s="14"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -5297,14 +5297,14 @@
     </row>
     <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>183</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="22"/>
+      <c r="E101" s="14"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -5322,25 +5322,25 @@
       <c r="T101" s="3"/>
     </row>
     <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="14" t="s">
+      <c r="A102" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="B102" s="15"/>
-      <c r="C102" s="15"/>
-      <c r="D102" s="15"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="23"/>
-      <c r="G102" s="23"/>
-      <c r="H102" s="23"/>
-      <c r="I102" s="23"/>
-      <c r="J102" s="23"/>
-      <c r="K102" s="23"/>
-      <c r="L102" s="23"/>
-      <c r="M102" s="23"/>
-      <c r="N102" s="23"/>
-      <c r="O102" s="23"/>
-      <c r="P102" s="23"/>
-      <c r="Q102" s="23"/>
+      <c r="B102" s="20"/>
+      <c r="C102" s="20"/>
+      <c r="D102" s="20"/>
+      <c r="E102" s="20"/>
+      <c r="F102" s="15"/>
+      <c r="G102" s="15"/>
+      <c r="H102" s="15"/>
+      <c r="I102" s="15"/>
+      <c r="J102" s="15"/>
+      <c r="K102" s="15"/>
+      <c r="L102" s="15"/>
+      <c r="M102" s="15"/>
+      <c r="N102" s="15"/>
+      <c r="O102" s="15"/>
+      <c r="P102" s="15"/>
+      <c r="Q102" s="15"/>
       <c r="R102" s="2"/>
       <c r="S102" s="2"/>
       <c r="T102" s="3" t="s">
@@ -5349,14 +5349,14 @@
     </row>
     <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="22"/>
+      <c r="E103" s="14"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -5375,14 +5375,14 @@
     </row>
     <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
-      <c r="E104" s="22"/>
+      <c r="E104" s="14"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -5401,14 +5401,14 @@
     </row>
     <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="12" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
-      <c r="E105" s="22"/>
+      <c r="E105" s="14"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -5427,14 +5427,14 @@
     </row>
     <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
-      <c r="E106" s="22"/>
+      <c r="E106" s="14"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -5453,14 +5453,14 @@
     </row>
     <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
-      <c r="E107" s="22"/>
+      <c r="E107" s="14"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -5479,7 +5479,7 @@
     </row>
     <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>64</v>
@@ -5505,7 +5505,7 @@
     </row>
     <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>65</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="12" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>66</v>
@@ -5557,7 +5557,7 @@
     </row>
     <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>67</v>
@@ -5583,7 +5583,7 @@
     </row>
     <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>68</v>
@@ -5609,14 +5609,14 @@
     </row>
     <row r="113" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
-      <c r="E113" s="22"/>
+      <c r="E113" s="14"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
@@ -5635,14 +5635,14 @@
     </row>
     <row r="114" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
-      <c r="E114" s="22"/>
+      <c r="E114" s="14"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
@@ -5660,25 +5660,25 @@
       <c r="T114" s="3"/>
     </row>
     <row r="115" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="14" t="s">
+      <c r="A115" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B115" s="15"/>
-      <c r="C115" s="15"/>
-      <c r="D115" s="15"/>
-      <c r="E115" s="15"/>
-      <c r="F115" s="23"/>
-      <c r="G115" s="23"/>
-      <c r="H115" s="23"/>
-      <c r="I115" s="23"/>
-      <c r="J115" s="23"/>
-      <c r="K115" s="23"/>
-      <c r="L115" s="23"/>
-      <c r="M115" s="23"/>
-      <c r="N115" s="23"/>
-      <c r="O115" s="23"/>
-      <c r="P115" s="23"/>
-      <c r="Q115" s="23"/>
+      <c r="B115" s="20"/>
+      <c r="C115" s="20"/>
+      <c r="D115" s="20"/>
+      <c r="E115" s="20"/>
+      <c r="F115" s="15"/>
+      <c r="G115" s="15"/>
+      <c r="H115" s="15"/>
+      <c r="I115" s="15"/>
+      <c r="J115" s="15"/>
+      <c r="K115" s="15"/>
+      <c r="L115" s="15"/>
+      <c r="M115" s="15"/>
+      <c r="N115" s="15"/>
+      <c r="O115" s="15"/>
+      <c r="P115" s="15"/>
+      <c r="Q115" s="15"/>
       <c r="R115" s="2"/>
       <c r="S115" s="2"/>
       <c r="T115" s="3" t="s">
@@ -5687,14 +5687,14 @@
     </row>
     <row r="116" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
-      <c r="E116" s="22"/>
+      <c r="E116" s="14"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -5713,14 +5713,14 @@
     </row>
     <row r="117" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="22"/>
+      <c r="E117" s="14"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -5739,14 +5739,14 @@
     </row>
     <row r="118" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
-      <c r="E118" s="22"/>
+      <c r="E118" s="14"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -5765,14 +5765,14 @@
     </row>
     <row r="119" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
-      <c r="E119" s="22"/>
+      <c r="E119" s="14"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -5791,14 +5791,14 @@
     </row>
     <row r="120" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
-      <c r="E120" s="22"/>
+      <c r="E120" s="14"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -5817,7 +5817,7 @@
     </row>
     <row r="121" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>77</v>
@@ -5843,7 +5843,7 @@
     </row>
     <row r="122" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>78</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="123" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>79</v>
@@ -5895,7 +5895,7 @@
     </row>
     <row r="124" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>80</v>
@@ -5921,7 +5921,7 @@
     </row>
     <row r="125" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>81</v>
@@ -5947,10 +5947,10 @@
     </row>
     <row r="126" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
@@ -5973,7 +5973,7 @@
     </row>
     <row r="127" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>82</v>
@@ -5999,14 +5999,14 @@
     </row>
     <row r="128" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
-      <c r="E128" s="22"/>
+      <c r="E128" s="14"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -6025,14 +6025,14 @@
     </row>
     <row r="129" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
-      <c r="E129" s="22"/>
+      <c r="E129" s="14"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -6051,14 +6051,14 @@
     </row>
     <row r="130" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
-      <c r="E130" s="22"/>
+      <c r="E130" s="14"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -6076,25 +6076,25 @@
       <c r="T130" s="3"/>
     </row>
     <row r="131" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="14" t="s">
+      <c r="A131" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B131" s="15"/>
-      <c r="C131" s="15"/>
-      <c r="D131" s="15"/>
-      <c r="E131" s="15"/>
-      <c r="F131" s="23"/>
-      <c r="G131" s="23"/>
-      <c r="H131" s="23"/>
-      <c r="I131" s="23"/>
-      <c r="J131" s="23"/>
-      <c r="K131" s="23"/>
-      <c r="L131" s="23"/>
-      <c r="M131" s="23"/>
-      <c r="N131" s="23"/>
-      <c r="O131" s="23"/>
-      <c r="P131" s="23"/>
-      <c r="Q131" s="23"/>
+      <c r="B131" s="20"/>
+      <c r="C131" s="20"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="20"/>
+      <c r="F131" s="15"/>
+      <c r="G131" s="15"/>
+      <c r="H131" s="15"/>
+      <c r="I131" s="15"/>
+      <c r="J131" s="15"/>
+      <c r="K131" s="15"/>
+      <c r="L131" s="15"/>
+      <c r="M131" s="15"/>
+      <c r="N131" s="15"/>
+      <c r="O131" s="15"/>
+      <c r="P131" s="15"/>
+      <c r="Q131" s="15"/>
       <c r="R131" s="2"/>
       <c r="S131" s="2"/>
       <c r="T131" s="3" t="s">
@@ -6103,14 +6103,14 @@
     </row>
     <row r="132" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
-      <c r="E132" s="22"/>
+      <c r="E132" s="14"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -6129,14 +6129,14 @@
     </row>
     <row r="133" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
-      <c r="E133" s="22"/>
+      <c r="E133" s="14"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -6155,14 +6155,14 @@
     </row>
     <row r="134" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
-      <c r="E134" s="22"/>
+      <c r="E134" s="14"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -6181,14 +6181,14 @@
     </row>
     <row r="135" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
-      <c r="E135" s="22"/>
+      <c r="E135" s="14"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -6207,14 +6207,14 @@
     </row>
     <row r="136" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
-      <c r="E136" s="22"/>
+      <c r="E136" s="14"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -6232,25 +6232,25 @@
       <c r="T136" s="3"/>
     </row>
     <row r="137" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="14" t="s">
+      <c r="A137" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B137" s="15"/>
-      <c r="C137" s="15"/>
-      <c r="D137" s="15"/>
-      <c r="E137" s="15"/>
-      <c r="F137" s="23"/>
-      <c r="G137" s="23"/>
-      <c r="H137" s="23"/>
-      <c r="I137" s="23"/>
-      <c r="J137" s="23"/>
-      <c r="K137" s="23"/>
-      <c r="L137" s="23"/>
-      <c r="M137" s="23"/>
-      <c r="N137" s="23"/>
-      <c r="O137" s="23"/>
-      <c r="P137" s="23"/>
-      <c r="Q137" s="23"/>
+      <c r="B137" s="20"/>
+      <c r="C137" s="20"/>
+      <c r="D137" s="20"/>
+      <c r="E137" s="20"/>
+      <c r="F137" s="15"/>
+      <c r="G137" s="15"/>
+      <c r="H137" s="15"/>
+      <c r="I137" s="15"/>
+      <c r="J137" s="15"/>
+      <c r="K137" s="15"/>
+      <c r="L137" s="15"/>
+      <c r="M137" s="15"/>
+      <c r="N137" s="15"/>
+      <c r="O137" s="15"/>
+      <c r="P137" s="15"/>
+      <c r="Q137" s="15"/>
       <c r="R137" s="2"/>
       <c r="S137" s="2"/>
       <c r="T137" s="3" t="s">
@@ -6259,14 +6259,14 @@
     </row>
     <row r="138" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
-      <c r="E138" s="22"/>
+      <c r="E138" s="14"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -6285,14 +6285,14 @@
     </row>
     <row r="139" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
-      <c r="E139" s="22"/>
+      <c r="E139" s="14"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -6310,25 +6310,25 @@
       <c r="T139" s="3"/>
     </row>
     <row r="140" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="14" t="s">
+      <c r="A140" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B140" s="15"/>
-      <c r="C140" s="15"/>
-      <c r="D140" s="15"/>
-      <c r="E140" s="15"/>
-      <c r="F140" s="23"/>
-      <c r="G140" s="23"/>
-      <c r="H140" s="23"/>
-      <c r="I140" s="23"/>
-      <c r="J140" s="23"/>
-      <c r="K140" s="23"/>
-      <c r="L140" s="23"/>
-      <c r="M140" s="23"/>
-      <c r="N140" s="23"/>
-      <c r="O140" s="23"/>
-      <c r="P140" s="23"/>
-      <c r="Q140" s="23"/>
+      <c r="B140" s="20"/>
+      <c r="C140" s="20"/>
+      <c r="D140" s="20"/>
+      <c r="E140" s="20"/>
+      <c r="F140" s="15"/>
+      <c r="G140" s="15"/>
+      <c r="H140" s="15"/>
+      <c r="I140" s="15"/>
+      <c r="J140" s="15"/>
+      <c r="K140" s="15"/>
+      <c r="L140" s="15"/>
+      <c r="M140" s="15"/>
+      <c r="N140" s="15"/>
+      <c r="O140" s="15"/>
+      <c r="P140" s="15"/>
+      <c r="Q140" s="15"/>
       <c r="R140" s="2"/>
       <c r="S140" s="2"/>
       <c r="T140" s="3" t="s">
@@ -6337,14 +6337,14 @@
     </row>
     <row r="141" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
-      <c r="E141" s="22"/>
+      <c r="E141" s="14"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -6363,14 +6363,14 @@
     </row>
     <row r="142" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
-      <c r="E142" s="22"/>
+      <c r="E142" s="14"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -6389,14 +6389,14 @@
     </row>
     <row r="143" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
-      <c r="E143" s="22"/>
+      <c r="E143" s="14"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -6415,14 +6415,14 @@
     </row>
     <row r="144" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
-      <c r="E144" s="22"/>
+      <c r="E144" s="14"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -6441,14 +6441,14 @@
     </row>
     <row r="145" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
-      <c r="E145" s="22"/>
+      <c r="E145" s="14"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -6467,14 +6467,14 @@
     </row>
     <row r="146" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
-      <c r="E146" s="22"/>
+      <c r="E146" s="14"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -6493,7 +6493,7 @@
     </row>
     <row r="147" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>23</v>
@@ -6519,7 +6519,7 @@
     </row>
     <row r="148" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>24</v>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="149" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>25</v>
@@ -6571,7 +6571,7 @@
     </row>
     <row r="150" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>26</v>
@@ -6597,7 +6597,7 @@
     </row>
     <row r="151" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>27</v>
@@ -6623,7 +6623,7 @@
     </row>
     <row r="152" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="12" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>28</v>
@@ -6649,7 +6649,7 @@
     </row>
     <row r="153" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="12" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>29</v>
@@ -6675,7 +6675,7 @@
     </row>
     <row r="154" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="12" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>30</v>
@@ -6701,7 +6701,7 @@
     </row>
     <row r="155" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>31</v>
@@ -6727,7 +6727,7 @@
     </row>
     <row r="156" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>32</v>
@@ -6753,7 +6753,7 @@
     </row>
     <row r="157" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>33</v>
@@ -6779,7 +6779,7 @@
     </row>
     <row r="158" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>34</v>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="159" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>35</v>
@@ -6831,7 +6831,7 @@
     </row>
     <row r="160" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>36</v>
@@ -6857,7 +6857,7 @@
     </row>
     <row r="161" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>37</v>
@@ -6883,7 +6883,7 @@
     </row>
     <row r="162" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>38</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="163" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>39</v>
@@ -6935,7 +6935,7 @@
     </row>
     <row r="164" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>40</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="165" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>41</v>
@@ -6987,7 +6987,7 @@
     </row>
     <row r="166" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>42</v>
@@ -7013,7 +7013,7 @@
     </row>
     <row r="167" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>43</v>
@@ -7039,7 +7039,7 @@
     </row>
     <row r="168" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>44</v>
@@ -7065,7 +7065,7 @@
     </row>
     <row r="169" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>45</v>
@@ -7091,7 +7091,7 @@
     </row>
     <row r="170" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>46</v>
@@ -7117,14 +7117,14 @@
     </row>
     <row r="171" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
-      <c r="E171" s="22"/>
+      <c r="E171" s="14"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
@@ -7143,14 +7143,14 @@
     </row>
     <row r="172" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
-      <c r="E172" s="22"/>
+      <c r="E172" s="14"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
@@ -7168,25 +7168,25 @@
       <c r="T172" s="3"/>
     </row>
     <row r="173" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="14" t="s">
+      <c r="A173" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B173" s="15"/>
-      <c r="C173" s="15"/>
-      <c r="D173" s="15"/>
-      <c r="E173" s="15"/>
-      <c r="F173" s="23"/>
-      <c r="G173" s="23"/>
-      <c r="H173" s="23"/>
-      <c r="I173" s="23"/>
-      <c r="J173" s="23"/>
-      <c r="K173" s="23"/>
-      <c r="L173" s="23"/>
-      <c r="M173" s="23"/>
-      <c r="N173" s="23"/>
-      <c r="O173" s="23"/>
-      <c r="P173" s="23"/>
-      <c r="Q173" s="23"/>
+      <c r="B173" s="20"/>
+      <c r="C173" s="20"/>
+      <c r="D173" s="20"/>
+      <c r="E173" s="20"/>
+      <c r="F173" s="15"/>
+      <c r="G173" s="15"/>
+      <c r="H173" s="15"/>
+      <c r="I173" s="15"/>
+      <c r="J173" s="15"/>
+      <c r="K173" s="15"/>
+      <c r="L173" s="15"/>
+      <c r="M173" s="15"/>
+      <c r="N173" s="15"/>
+      <c r="O173" s="15"/>
+      <c r="P173" s="15"/>
+      <c r="Q173" s="15"/>
       <c r="R173" s="2"/>
       <c r="S173" s="2"/>
       <c r="T173" s="3" t="s">
@@ -7195,14 +7195,14 @@
     </row>
     <row r="174" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="12" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
-      <c r="E174" s="22"/>
+      <c r="E174" s="14"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
@@ -7221,14 +7221,14 @@
     </row>
     <row r="175" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
-      <c r="E175" s="22"/>
+      <c r="E175" s="14"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
@@ -7247,14 +7247,14 @@
     </row>
     <row r="176" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="12" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
-      <c r="E176" s="22"/>
+      <c r="E176" s="14"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
@@ -7273,14 +7273,14 @@
     </row>
     <row r="177" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
-      <c r="E177" s="22"/>
+      <c r="E177" s="14"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
@@ -7299,14 +7299,14 @@
     </row>
     <row r="178" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="12" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
-      <c r="E178" s="22"/>
+      <c r="E178" s="14"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
@@ -7325,14 +7325,14 @@
     </row>
     <row r="179" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="12" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
-      <c r="E179" s="22"/>
+      <c r="E179" s="14"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
@@ -7351,14 +7351,14 @@
     </row>
     <row r="180" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
-      <c r="E180" s="22"/>
+      <c r="E180" s="14"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
@@ -7377,7 +7377,7 @@
     </row>
     <row r="181" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>93</v>
@@ -7403,7 +7403,7 @@
     </row>
     <row r="182" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>94</v>
@@ -7429,7 +7429,7 @@
     </row>
     <row r="183" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>95</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="184" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>96</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="185" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="12" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>97</v>
@@ -7507,7 +7507,7 @@
     </row>
     <row r="186" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="12" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>98</v>
@@ -7533,7 +7533,7 @@
     </row>
     <row r="187" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>99</v>
@@ -7559,7 +7559,7 @@
     </row>
     <row r="188" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="12" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>100</v>
@@ -7585,7 +7585,7 @@
     </row>
     <row r="189" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="12" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>101</v>
@@ -7611,7 +7611,7 @@
     </row>
     <row r="190" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="12" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>102</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="191" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="12" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>103</v>
@@ -7663,7 +7663,7 @@
     </row>
     <row r="192" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>104</v>
@@ -7689,7 +7689,7 @@
     </row>
     <row r="193" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="12" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>105</v>
@@ -7715,7 +7715,7 @@
     </row>
     <row r="194" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="12" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>106</v>
@@ -7741,7 +7741,7 @@
     </row>
     <row r="195" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>107</v>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="196" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="12" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>108</v>
@@ -7793,7 +7793,7 @@
     </row>
     <row r="197" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="12" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>109</v>
@@ -7819,7 +7819,7 @@
     </row>
     <row r="198" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="12" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>110</v>
@@ -7845,7 +7845,7 @@
     </row>
     <row r="199" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>111</v>
@@ -7871,14 +7871,14 @@
     </row>
     <row r="200" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="12" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
-      <c r="E200" s="22"/>
+      <c r="E200" s="14"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
@@ -7897,14 +7897,14 @@
     </row>
     <row r="201" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
-      <c r="E201" s="22"/>
+      <c r="E201" s="14"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
@@ -7922,25 +7922,25 @@
       <c r="T201" s="3"/>
     </row>
     <row r="202" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="14" t="s">
+      <c r="A202" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B202" s="15"/>
-      <c r="C202" s="15"/>
-      <c r="D202" s="15"/>
-      <c r="E202" s="15"/>
-      <c r="F202" s="23"/>
-      <c r="G202" s="23"/>
-      <c r="H202" s="23"/>
-      <c r="I202" s="23"/>
-      <c r="J202" s="23"/>
-      <c r="K202" s="23"/>
-      <c r="L202" s="23"/>
-      <c r="M202" s="23"/>
-      <c r="N202" s="23"/>
-      <c r="O202" s="23"/>
-      <c r="P202" s="23"/>
-      <c r="Q202" s="23"/>
+      <c r="B202" s="20"/>
+      <c r="C202" s="20"/>
+      <c r="D202" s="20"/>
+      <c r="E202" s="20"/>
+      <c r="F202" s="15"/>
+      <c r="G202" s="15"/>
+      <c r="H202" s="15"/>
+      <c r="I202" s="15"/>
+      <c r="J202" s="15"/>
+      <c r="K202" s="15"/>
+      <c r="L202" s="15"/>
+      <c r="M202" s="15"/>
+      <c r="N202" s="15"/>
+      <c r="O202" s="15"/>
+      <c r="P202" s="15"/>
+      <c r="Q202" s="15"/>
       <c r="R202" s="2"/>
       <c r="S202" s="2"/>
       <c r="T202" s="3" t="s">
@@ -7949,14 +7949,14 @@
     </row>
     <row r="203" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
-      <c r="E203" s="22"/>
+      <c r="E203" s="14"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
@@ -7975,14 +7975,14 @@
     </row>
     <row r="204" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
-      <c r="E204" s="22"/>
+      <c r="E204" s="14"/>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
@@ -8001,14 +8001,14 @@
     </row>
     <row r="205" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="12" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
-      <c r="E205" s="22"/>
+      <c r="E205" s="14"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
@@ -8027,14 +8027,14 @@
     </row>
     <row r="206" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
-      <c r="E206" s="22"/>
+      <c r="E206" s="14"/>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
@@ -8053,14 +8053,14 @@
     </row>
     <row r="207" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
-      <c r="E207" s="22"/>
+      <c r="E207" s="14"/>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
@@ -8079,14 +8079,14 @@
     </row>
     <row r="208" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="12" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
-      <c r="E208" s="22"/>
+      <c r="E208" s="14"/>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="209" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="12" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>121</v>
@@ -8131,7 +8131,7 @@
     </row>
     <row r="210" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="12" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>122</v>
@@ -8157,7 +8157,7 @@
     </row>
     <row r="211" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>123</v>
@@ -8183,7 +8183,7 @@
     </row>
     <row r="212" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="12" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>124</v>
@@ -8209,7 +8209,7 @@
     </row>
     <row r="213" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="12" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>125</v>
@@ -8235,7 +8235,7 @@
     </row>
     <row r="214" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="12" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>126</v>
@@ -8261,7 +8261,7 @@
     </row>
     <row r="215" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="12" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>127</v>
@@ -8287,7 +8287,7 @@
     </row>
     <row r="216" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="12" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>128</v>
@@ -8313,7 +8313,7 @@
     </row>
     <row r="217" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="12" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>129</v>
@@ -8339,7 +8339,7 @@
     </row>
     <row r="218" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>130</v>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="219" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="12" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>131</v>
@@ -8391,14 +8391,14 @@
     </row>
     <row r="220" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
-      <c r="E220" s="22"/>
+      <c r="E220" s="14"/>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
@@ -8417,14 +8417,14 @@
     </row>
     <row r="221" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="12" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
-      <c r="E221" s="22"/>
+      <c r="E221" s="14"/>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
@@ -8443,14 +8443,14 @@
     </row>
     <row r="222" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
-      <c r="E222" s="22"/>
+      <c r="E222" s="14"/>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
@@ -8468,25 +8468,25 @@
       <c r="T222" s="3"/>
     </row>
     <row r="223" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="14" t="s">
+      <c r="A223" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B223" s="15"/>
-      <c r="C223" s="15"/>
-      <c r="D223" s="15"/>
-      <c r="E223" s="15"/>
-      <c r="F223" s="23"/>
-      <c r="G223" s="23"/>
-      <c r="H223" s="23"/>
-      <c r="I223" s="23"/>
-      <c r="J223" s="23"/>
-      <c r="K223" s="23"/>
-      <c r="L223" s="23"/>
-      <c r="M223" s="23"/>
-      <c r="N223" s="23"/>
-      <c r="O223" s="23"/>
-      <c r="P223" s="23"/>
-      <c r="Q223" s="23"/>
+      <c r="B223" s="20"/>
+      <c r="C223" s="20"/>
+      <c r="D223" s="20"/>
+      <c r="E223" s="20"/>
+      <c r="F223" s="15"/>
+      <c r="G223" s="15"/>
+      <c r="H223" s="15"/>
+      <c r="I223" s="15"/>
+      <c r="J223" s="15"/>
+      <c r="K223" s="15"/>
+      <c r="L223" s="15"/>
+      <c r="M223" s="15"/>
+      <c r="N223" s="15"/>
+      <c r="O223" s="15"/>
+      <c r="P223" s="15"/>
+      <c r="Q223" s="15"/>
       <c r="R223" s="2"/>
       <c r="S223" s="2"/>
       <c r="T223" s="3" t="s">
@@ -8495,14 +8495,14 @@
     </row>
     <row r="224" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>255</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
-      <c r="E224" s="22"/>
+      <c r="E224" s="14"/>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
@@ -8521,14 +8521,14 @@
     </row>
     <row r="225" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="12" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>256</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
-      <c r="E225" s="22"/>
+      <c r="E225" s="14"/>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
@@ -8547,14 +8547,14 @@
     </row>
     <row r="226" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="12" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>257</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
-      <c r="E226" s="22"/>
+      <c r="E226" s="14"/>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
@@ -8573,14 +8573,14 @@
     </row>
     <row r="227" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>258</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
-      <c r="E227" s="22"/>
+      <c r="E227" s="14"/>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
@@ -8599,14 +8599,14 @@
     </row>
     <row r="228" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="12" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>259</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
-      <c r="E228" s="22"/>
+      <c r="E228" s="14"/>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
@@ -8625,14 +8625,14 @@
     </row>
     <row r="229" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>260</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
-      <c r="E229" s="22"/>
+      <c r="E229" s="14"/>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
@@ -8651,14 +8651,14 @@
     </row>
     <row r="230" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="12" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>261</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
-      <c r="E230" s="22"/>
+      <c r="E230" s="14"/>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
@@ -8677,7 +8677,7 @@
     </row>
     <row r="231" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="12" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>262</v>
@@ -8703,7 +8703,7 @@
     </row>
     <row r="232" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>263</v>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="233" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>264</v>
@@ -8755,7 +8755,7 @@
     </row>
     <row r="234" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>265</v>
@@ -8781,7 +8781,7 @@
     </row>
     <row r="235" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="12" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>266</v>
@@ -8807,7 +8807,7 @@
     </row>
     <row r="236" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="12" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>267</v>
@@ -8833,7 +8833,7 @@
     </row>
     <row r="237" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>268</v>
@@ -8859,7 +8859,7 @@
     </row>
     <row r="238" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="12" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>269</v>
@@ -8885,7 +8885,7 @@
     </row>
     <row r="239" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="12" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>270</v>
@@ -8911,7 +8911,7 @@
     </row>
     <row r="240" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="12" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>271</v>
@@ -8937,14 +8937,14 @@
     </row>
     <row r="241" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>272</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
-      <c r="E241" s="22"/>
+      <c r="E241" s="14"/>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
@@ -8963,14 +8963,14 @@
     </row>
     <row r="242" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>273</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
-      <c r="E242" s="22"/>
+      <c r="E242" s="14"/>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
@@ -8989,14 +8989,14 @@
     </row>
     <row r="243" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>274</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
-      <c r="E243" s="22"/>
+      <c r="E243" s="14"/>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
@@ -9014,25 +9014,25 @@
       <c r="T243" s="3"/>
     </row>
     <row r="244" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="14" t="s">
+      <c r="A244" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="B244" s="15"/>
-      <c r="C244" s="15"/>
-      <c r="D244" s="15"/>
-      <c r="E244" s="15"/>
-      <c r="F244" s="23"/>
-      <c r="G244" s="23"/>
-      <c r="H244" s="23"/>
-      <c r="I244" s="23"/>
-      <c r="J244" s="23"/>
-      <c r="K244" s="23"/>
-      <c r="L244" s="23"/>
-      <c r="M244" s="23"/>
-      <c r="N244" s="23"/>
-      <c r="O244" s="23"/>
-      <c r="P244" s="23"/>
-      <c r="Q244" s="23"/>
+      <c r="B244" s="20"/>
+      <c r="C244" s="20"/>
+      <c r="D244" s="20"/>
+      <c r="E244" s="20"/>
+      <c r="F244" s="15"/>
+      <c r="G244" s="15"/>
+      <c r="H244" s="15"/>
+      <c r="I244" s="15"/>
+      <c r="J244" s="15"/>
+      <c r="K244" s="15"/>
+      <c r="L244" s="15"/>
+      <c r="M244" s="15"/>
+      <c r="N244" s="15"/>
+      <c r="O244" s="15"/>
+      <c r="P244" s="15"/>
+      <c r="Q244" s="15"/>
       <c r="R244" s="2"/>
       <c r="S244" s="2"/>
       <c r="T244" s="3" t="s">
@@ -9041,14 +9041,14 @@
     </row>
     <row r="245" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
-      <c r="E245" s="22"/>
+      <c r="E245" s="14"/>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
@@ -9067,14 +9067,14 @@
     </row>
     <row r="246" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
-      <c r="E246" s="22"/>
+      <c r="E246" s="14"/>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
@@ -9093,14 +9093,14 @@
     </row>
     <row r="247" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="12" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
-      <c r="E247" s="22"/>
+      <c r="E247" s="14"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
@@ -9119,14 +9119,14 @@
     </row>
     <row r="248" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
-      <c r="E248" s="22"/>
+      <c r="E248" s="14"/>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
@@ -9145,14 +9145,14 @@
     </row>
     <row r="249" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="12" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
-      <c r="E249" s="22"/>
+      <c r="E249" s="14"/>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
@@ -9171,14 +9171,14 @@
     </row>
     <row r="250" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="12" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
-      <c r="E250" s="22"/>
+      <c r="E250" s="14"/>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
@@ -9197,7 +9197,7 @@
     </row>
     <row r="251" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="12" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>142</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="252" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="12" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>143</v>
@@ -9249,7 +9249,7 @@
     </row>
     <row r="253" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>144</v>
@@ -9275,7 +9275,7 @@
     </row>
     <row r="254" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="12" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>145</v>
@@ -9301,7 +9301,7 @@
     </row>
     <row r="255" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>146</v>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="256" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>147</v>
@@ -9353,14 +9353,14 @@
     </row>
     <row r="257" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
-      <c r="E257" s="22"/>
+      <c r="E257" s="14"/>
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
@@ -9379,14 +9379,14 @@
     </row>
     <row r="258" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="12" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
-      <c r="E258" s="22"/>
+      <c r="E258" s="14"/>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
@@ -9404,25 +9404,25 @@
       <c r="T258" s="3"/>
     </row>
     <row r="259" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="14" t="s">
+      <c r="A259" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="B259" s="15"/>
-      <c r="C259" s="15"/>
-      <c r="D259" s="15"/>
-      <c r="E259" s="15"/>
-      <c r="F259" s="23"/>
-      <c r="G259" s="23"/>
-      <c r="H259" s="23"/>
-      <c r="I259" s="23"/>
-      <c r="J259" s="23"/>
-      <c r="K259" s="23"/>
-      <c r="L259" s="23"/>
-      <c r="M259" s="23"/>
-      <c r="N259" s="23"/>
-      <c r="O259" s="23"/>
-      <c r="P259" s="23"/>
-      <c r="Q259" s="23"/>
+      <c r="B259" s="20"/>
+      <c r="C259" s="20"/>
+      <c r="D259" s="20"/>
+      <c r="E259" s="20"/>
+      <c r="F259" s="15"/>
+      <c r="G259" s="15"/>
+      <c r="H259" s="15"/>
+      <c r="I259" s="15"/>
+      <c r="J259" s="15"/>
+      <c r="K259" s="15"/>
+      <c r="L259" s="15"/>
+      <c r="M259" s="15"/>
+      <c r="N259" s="15"/>
+      <c r="O259" s="15"/>
+      <c r="P259" s="15"/>
+      <c r="Q259" s="15"/>
       <c r="R259" s="2"/>
       <c r="S259" s="2"/>
       <c r="T259" s="3" t="s">
@@ -9431,14 +9431,14 @@
     </row>
     <row r="260" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="12" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
-      <c r="E260" s="22"/>
+      <c r="E260" s="14"/>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
@@ -9457,14 +9457,14 @@
     </row>
     <row r="261" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="12" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>231</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
-      <c r="E261" s="22"/>
+      <c r="E261" s="14"/>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
@@ -9483,14 +9483,14 @@
     </row>
     <row r="262" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="12" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>232</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
-      <c r="E262" s="22"/>
+      <c r="E262" s="14"/>
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
@@ -9509,14 +9509,14 @@
     </row>
     <row r="263" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="12" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>233</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
-      <c r="E263" s="22"/>
+      <c r="E263" s="14"/>
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
@@ -9535,14 +9535,14 @@
     </row>
     <row r="264" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>234</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
-      <c r="E264" s="22"/>
+      <c r="E264" s="14"/>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
@@ -9561,7 +9561,7 @@
     </row>
     <row r="265" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="12" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>235</v>
@@ -9587,7 +9587,7 @@
     </row>
     <row r="266" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="12" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>236</v>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="267" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="12" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>237</v>
@@ -9639,7 +9639,7 @@
     </row>
     <row r="268" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="12" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>238</v>
@@ -9665,7 +9665,7 @@
     </row>
     <row r="269" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>239</v>
@@ -9691,7 +9691,7 @@
     </row>
     <row r="270" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>240</v>
@@ -9717,7 +9717,7 @@
     </row>
     <row r="271" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="12" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>241</v>
@@ -9743,7 +9743,7 @@
     </row>
     <row r="272" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="12" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>242</v>
@@ -9769,7 +9769,7 @@
     </row>
     <row r="273" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="12" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>243</v>
@@ -9795,7 +9795,7 @@
     </row>
     <row r="274" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="12" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>244</v>
@@ -9821,14 +9821,14 @@
     </row>
     <row r="275" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="12" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>245</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
-      <c r="E275" s="22"/>
+      <c r="E275" s="14"/>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
@@ -9847,14 +9847,14 @@
     </row>
     <row r="276" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="12" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>246</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
-      <c r="E276" s="22"/>
+      <c r="E276" s="14"/>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
@@ -9872,25 +9872,25 @@
       <c r="T276" s="3"/>
     </row>
     <row r="277" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="14" t="s">
+      <c r="A277" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="B277" s="15"/>
-      <c r="C277" s="15"/>
-      <c r="D277" s="15"/>
-      <c r="E277" s="15"/>
-      <c r="F277" s="23"/>
-      <c r="G277" s="23"/>
-      <c r="H277" s="23"/>
-      <c r="I277" s="23"/>
-      <c r="J277" s="23"/>
-      <c r="K277" s="23"/>
-      <c r="L277" s="23"/>
-      <c r="M277" s="23"/>
-      <c r="N277" s="23"/>
-      <c r="O277" s="23"/>
-      <c r="P277" s="23"/>
-      <c r="Q277" s="23"/>
+      <c r="B277" s="20"/>
+      <c r="C277" s="20"/>
+      <c r="D277" s="20"/>
+      <c r="E277" s="20"/>
+      <c r="F277" s="15"/>
+      <c r="G277" s="15"/>
+      <c r="H277" s="15"/>
+      <c r="I277" s="15"/>
+      <c r="J277" s="15"/>
+      <c r="K277" s="15"/>
+      <c r="L277" s="15"/>
+      <c r="M277" s="15"/>
+      <c r="N277" s="15"/>
+      <c r="O277" s="15"/>
+      <c r="P277" s="15"/>
+      <c r="Q277" s="15"/>
       <c r="R277" s="2"/>
       <c r="S277" s="2"/>
       <c r="T277" s="3" t="s">
@@ -9899,14 +9899,14 @@
     </row>
     <row r="278" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="12" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>248</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
-      <c r="E278" s="22"/>
+      <c r="E278" s="14"/>
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
@@ -9925,14 +9925,14 @@
     </row>
     <row r="279" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="12" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>249</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
-      <c r="E279" s="22"/>
+      <c r="E279" s="14"/>
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
@@ -9951,7 +9951,7 @@
     </row>
     <row r="280" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="12" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>250</v>
@@ -9977,14 +9977,14 @@
     </row>
     <row r="281" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="12" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>251</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
-      <c r="E281" s="22"/>
+      <c r="E281" s="14"/>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
@@ -10003,14 +10003,14 @@
     </row>
     <row r="282" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="12" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>252</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
-      <c r="E282" s="22"/>
+      <c r="E282" s="14"/>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
@@ -10029,14 +10029,14 @@
     </row>
     <row r="283" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="12" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>253</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
-      <c r="E283" s="22"/>
+      <c r="E283" s="14"/>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
@@ -10054,25 +10054,25 @@
       <c r="T283" s="3"/>
     </row>
     <row r="284" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="14" t="s">
+      <c r="A284" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="B284" s="15"/>
-      <c r="C284" s="15"/>
-      <c r="D284" s="15"/>
-      <c r="E284" s="15"/>
-      <c r="F284" s="23"/>
-      <c r="G284" s="23"/>
-      <c r="H284" s="23"/>
-      <c r="I284" s="23"/>
-      <c r="J284" s="23"/>
-      <c r="K284" s="23"/>
-      <c r="L284" s="23"/>
-      <c r="M284" s="23"/>
-      <c r="N284" s="23"/>
-      <c r="O284" s="23"/>
-      <c r="P284" s="23"/>
-      <c r="Q284" s="23"/>
+      <c r="B284" s="20"/>
+      <c r="C284" s="20"/>
+      <c r="D284" s="20"/>
+      <c r="E284" s="20"/>
+      <c r="F284" s="15"/>
+      <c r="G284" s="15"/>
+      <c r="H284" s="15"/>
+      <c r="I284" s="15"/>
+      <c r="J284" s="15"/>
+      <c r="K284" s="15"/>
+      <c r="L284" s="15"/>
+      <c r="M284" s="15"/>
+      <c r="N284" s="15"/>
+      <c r="O284" s="15"/>
+      <c r="P284" s="15"/>
+      <c r="Q284" s="15"/>
       <c r="R284" s="2"/>
       <c r="S284" s="2"/>
       <c r="T284" s="3" t="s">
@@ -10080,31 +10080,36 @@
       </c>
     </row>
     <row r="285" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A285" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="B285" s="21"/>
-      <c r="C285" s="21"/>
-      <c r="D285" s="21"/>
-      <c r="E285" s="21"/>
-      <c r="F285" s="24"/>
-      <c r="G285" s="24"/>
-      <c r="H285" s="24"/>
-      <c r="I285" s="24"/>
-      <c r="J285" s="24"/>
-      <c r="K285" s="24"/>
-      <c r="L285" s="24"/>
-      <c r="M285" s="24"/>
-      <c r="N285" s="24"/>
-      <c r="O285" s="24"/>
-      <c r="P285" s="24"/>
-      <c r="Q285" s="24"/>
+      <c r="A285" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="B285" s="18"/>
+      <c r="C285" s="18"/>
+      <c r="D285" s="18"/>
+      <c r="E285" s="18"/>
+      <c r="F285" s="16"/>
+      <c r="G285" s="16"/>
+      <c r="H285" s="16"/>
+      <c r="I285" s="16"/>
+      <c r="J285" s="16"/>
+      <c r="K285" s="16"/>
+      <c r="L285" s="16"/>
+      <c r="M285" s="16"/>
+      <c r="N285" s="16"/>
+      <c r="O285" s="16"/>
+      <c r="P285" s="16"/>
+      <c r="Q285" s="16"/>
       <c r="R285" s="4"/>
       <c r="S285" s="4"/>
       <c r="T285" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A2:T3"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="N5:R5"/>
+    <mergeCell ref="N6:R6"/>
     <mergeCell ref="A285:E285"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A22:E22"/>
@@ -10121,11 +10126,6 @@
     <mergeCell ref="A259:E259"/>
     <mergeCell ref="A277:E277"/>
     <mergeCell ref="A284:E284"/>
-    <mergeCell ref="A2:T3"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="N5:R5"/>
-    <mergeCell ref="N6:R6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
